--- a/forms/trg/Formulir_TRG_milkd.xlsx
+++ b/forms/trg/Formulir_TRG_milkd.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="12" t="n"/>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
